--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104740_W32.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104740_W32.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2723</v>
+        <v>4.7524</v>
       </c>
       <c r="E2" t="n">
-        <v>0.167</v>
+        <v>0.5598</v>
       </c>
       <c r="F2" t="n">
-        <v>5.1053</v>
+        <v>4.1926</v>
       </c>
       <c r="G2" t="n">
-        <v>1.9977</v>
+        <v>1.9881</v>
       </c>
       <c r="H2" t="n">
-        <v>2.0663</v>
+        <v>2.0549</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.06859999999999999</v>
+        <v>-0.0668</v>
       </c>
       <c r="J2" t="n">
-        <v>1.5871</v>
+        <v>1.5661</v>
       </c>
       <c r="K2" t="n">
-        <v>1.4127</v>
+        <v>1.3952</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1744</v>
+        <v>0.1708</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4106</v>
+        <v>0.422</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6536</v>
+        <v>0.6597</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.243</v>
+        <v>-0.2377</v>
       </c>
       <c r="P2" t="n">
-        <v>2.9534</v>
+        <v>2.9592</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.9534</v>
+        <v>2.9592</v>
       </c>
       <c r="S2" t="n">
-        <v>1.161</v>
+        <v>0.6505</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5803</v>
+        <v>-0.1609</v>
       </c>
       <c r="U2" t="n">
-        <v>1.7412</v>
+        <v>0.8113</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.8398</v>
+        <v>-0.8454</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.8398</v>
+        <v>-0.8454</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. AGADA</t>
+          <t>J. BATEMON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5287</v>
+        <v>1.7209</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9370000000000001</v>
+        <v>1.3021</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5917</v>
+        <v>0.4188</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.1176</v>
+        <v>-1.3268</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1803</v>
+        <v>2.3647</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9374</v>
+        <v>-3.6915</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.5261</v>
+        <v>-0.6882</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.5634</v>
+        <v>1.5471</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0373</v>
+        <v>-2.2353</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5915</v>
+        <v>-0.6385999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3831</v>
+        <v>0.8176</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9746</v>
+        <v>-1.4562</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3631</v>
+        <v>2.0487</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3631</v>
+        <v>2.0487</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6694</v>
+        <v>0.0673</v>
       </c>
       <c r="T3" t="n">
-        <v>1.8494</v>
+        <v>-0.1886</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.18</v>
+        <v>0.2559</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3862</v>
+        <v>0.9317</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3862</v>
+        <v>2.1789</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. BATEMON</t>
+          <t>C. WALDEN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1639</v>
+        <v>1.3958</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1431</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0209</v>
+        <v>1.2991</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.318</v>
+        <v>0.6862</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3736</v>
+        <v>0.3704</v>
       </c>
       <c r="I4" t="n">
-        <v>-3.6915</v>
+        <v>0.3159</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.6674</v>
+        <v>0.0689</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5622</v>
+        <v>0.0689</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.2296</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6506</v>
+        <v>0.6173</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8114</v>
+        <v>0.3014</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.4619</v>
+        <v>0.3159</v>
       </c>
       <c r="P4" t="n">
-        <v>2.0447</v>
+        <v>0.6829</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0447</v>
+        <v>0.6829</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4946</v>
+        <v>0.0267</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.372</v>
+        <v>0.0278</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1226</v>
+        <v>-0.0011</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9318</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2.1825</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.15</v>
+        <v>1.0506</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9009</v>
+        <v>1.7262</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.751</v>
+        <v>-0.6756</v>
       </c>
       <c r="G5" t="n">
         <v>1.8026</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5643</v>
+        <v>1.5625</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2383</v>
+        <v>0.2401</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4889</v>
+        <v>1.4851</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4516</v>
+        <v>1.4479</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3137</v>
+        <v>0.3174</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1127</v>
+        <v>0.1146</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2011</v>
+        <v>0.2028</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3257</v>
+        <v>0.2206</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2526</v>
+        <v>0.0834</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0731</v>
+        <v>0.1372</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.5687</v>
+        <v>-2.5659</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.7281</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. WALDEN</t>
+          <t>C. KRUTWIG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0632</v>
+        <v>0.8015</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1391</v>
+        <v>-0.4911</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2023</v>
+        <v>1.2926</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6852</v>
+        <v>0.6563</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3697</v>
+        <v>2.7635</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3156</v>
+        <v>-2.1072</v>
       </c>
       <c r="J6" t="n">
-        <v>0.06909999999999999</v>
+        <v>1.6673</v>
       </c>
       <c r="K6" t="n">
-        <v>0.06909999999999999</v>
+        <v>1.63</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.0372</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6161</v>
+        <v>-1.0109</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3005</v>
+        <v>1.1335</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3156</v>
+        <v>-2.1444</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6816</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6816</v>
+        <v>1.8211</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3035</v>
+        <v>0.6004</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2082</v>
+        <v>0.118</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0953</v>
+        <v>0.4824</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ</t>
+          <t>C. AGADA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2895</v>
+        <v>0.6896</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6784</v>
+        <v>-0.0707</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9679</v>
+        <v>0.7603</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7576000000000001</v>
+        <v>-1.1194</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2803</v>
+        <v>-0.1859</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.0379</v>
+        <v>-0.9335</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.584</v>
+        <v>-0.5358000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1676</v>
+        <v>-0.573</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7516</v>
+        <v>0.0372</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1736</v>
+        <v>-0.5836</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1127</v>
+        <v>0.3871</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2863</v>
+        <v>-0.9708</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.3658</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1359</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1359</v>
+        <v>1.3658</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0471</v>
+        <v>0.8302</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0415</v>
+        <v>0.852</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0056</v>
+        <v>-0.0218</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.387</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.387</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. KRUTWIG</t>
+          <t>A. RODRIGUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2835</v>
+        <v>-0.2582</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8947000000000001</v>
+        <v>-1.3297</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1782</v>
+        <v>1.0715</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6565</v>
+        <v>-0.7587</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7695</v>
+        <v>0.2762</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.113</v>
+        <v>-1.035</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6798</v>
+        <v>-0.5908</v>
       </c>
       <c r="K8" t="n">
-        <v>1.6425</v>
+        <v>0.1616</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0373</v>
+        <v>-0.7524</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0234</v>
+        <v>-0.168</v>
       </c>
       <c r="N8" t="n">
-        <v>1.127</v>
+        <v>0.1146</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.1503</v>
+        <v>-0.2826</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4544</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2719</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8175</v>
+        <v>1.1382</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0814</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3026</v>
+        <v>0.3992</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3841</v>
+        <v>0.1013</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. EJIM</t>
+          <t>J. SHURNA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1918</v>
+        <v>-0.8917</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.6999</v>
+        <v>-0.4383</v>
       </c>
       <c r="F9" t="n">
-        <v>3.5081</v>
+        <v>-0.4535</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9076</v>
+        <v>-1.8382</v>
       </c>
       <c r="H9" t="n">
-        <v>1.9903</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.8979</v>
+        <v>-2.3921</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.7061</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1639</v>
+        <v>0.1379</v>
       </c>
       <c r="L9" t="n">
-        <v>-3.8699</v>
+        <v>-0.7896</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7985</v>
+        <v>-1.1865</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8264</v>
+        <v>0.416</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0279</v>
+        <v>-1.6025</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6816</v>
+        <v>0.4553</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2719</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.9534</v>
+        <v>0.4553</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0342</v>
+        <v>0.4912</v>
       </c>
       <c r="T9" t="n">
-        <v>0.278</v>
+        <v>0.2135</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2438</v>
+        <v>0.2777</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. SHURNA</t>
+          <t>M. EJIM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6595</v>
+        <v>-1.2263</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9787</v>
+        <v>-5.0041</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6808</v>
+        <v>3.7778</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.8432</v>
+        <v>-1.9068</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5515</v>
+        <v>1.9902</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.3947</v>
+        <v>-3.897</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6506999999999999</v>
+        <v>-2.7156</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1383</v>
+        <v>1.1581</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7889</v>
+        <v>-3.8737</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1925</v>
+        <v>0.8088</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4132</v>
+        <v>0.832</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.6058</v>
+        <v>-0.0232</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4544</v>
+        <v>0.6829</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4544</v>
+        <v>2.9592</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2707</v>
+        <v>-0.0024</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3281</v>
+        <v>-0.0122</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0574</v>
+        <v>0.0097</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6943</v>
+        <v>-1.4519</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6333</v>
+        <v>-1.3342</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.061</v>
+        <v>-0.1177</v>
       </c>
       <c r="G11" t="n">
-        <v>1.2056</v>
+        <v>1.2054</v>
       </c>
       <c r="H11" t="n">
-        <v>1.4779</v>
+        <v>1.4763</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2723</v>
+        <v>-0.271</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8468</v>
+        <v>0.8446</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8468</v>
+        <v>0.8446</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3588</v>
+        <v>0.3608</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6311</v>
+        <v>0.6317</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2723</v>
+        <v>-0.271</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.8175</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S11" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.2532</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2082</v>
+        <v>0.0975</v>
       </c>
       <c r="U11" t="n">
-        <v>0.217</v>
+        <v>0.1557</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9664</v>
+        <v>-2.6532</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.5039</v>
+        <v>-2.866</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5375</v>
+        <v>0.2128</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0493</v>
+        <v>-0.0528</v>
       </c>
       <c r="H12" t="n">
-        <v>1.5764</v>
+        <v>1.569</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.6257</v>
+        <v>-1.6218</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7872</v>
+        <v>0.7742</v>
       </c>
       <c r="K12" t="n">
-        <v>0.75</v>
+        <v>0.737</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8366</v>
+        <v>-0.827</v>
       </c>
       <c r="N12" t="n">
-        <v>0.8264</v>
+        <v>0.832</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.663</v>
+        <v>-1.659</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.8175</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.4078</v>
+        <v>-3.4145</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0083</v>
+        <v>0.3101</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8833</v>
+        <v>-0.2257</v>
       </c>
       <c r="U12" t="n">
-        <v>0.875</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.239100000000001</v>
+        <v>3.929499999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.380000000000001</v>
+        <v>-7.849299999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>11.6191</v>
+        <v>11.7787</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.6457000000000001</v>
+        <v>-0.6640999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>14.8395</v>
+        <v>14.7957</v>
       </c>
       <c r="I13" t="n">
-        <v>-15.4851</v>
+        <v>-15.4599</v>
       </c>
       <c r="J13" t="n">
-        <v>1.3246</v>
+        <v>1.2241</v>
       </c>
       <c r="K13" t="n">
-        <v>8.641300000000001</v>
+        <v>8.555299999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>-7.3164</v>
+        <v>-7.3314</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.9705</v>
+        <v>-1.8883</v>
       </c>
       <c r="N13" t="n">
-        <v>6.1981</v>
+        <v>6.2402</v>
       </c>
       <c r="O13" t="n">
-        <v>-8.1684</v>
+        <v>-8.1287</v>
       </c>
       <c r="P13" t="n">
-        <v>5.679699999999999</v>
+        <v>5.690700000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>-11.3594</v>
+        <v>-11.3816</v>
       </c>
       <c r="R13" t="n">
-        <v>17.039</v>
+        <v>17.0725</v>
       </c>
       <c r="S13" t="n">
-        <v>3.2505</v>
+        <v>3.9483</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5388000000000002</v>
+        <v>1.204</v>
       </c>
       <c r="U13" t="n">
-        <v>2.7117</v>
+        <v>2.7441</v>
       </c>
       <c r="V13" t="n">
-        <v>-5.045500000000001</v>
+        <v>-5.0456</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1159</v>
+        <v>1.1043</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.1614</v>
+        <v>-6.149900000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.2154</v>
+        <v>3.6586</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2386</v>
+        <v>2.0318</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9767</v>
+        <v>1.6268</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4774</v>
+        <v>0.4751</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.5297</v>
+        <v>-1.528</v>
       </c>
       <c r="I14" t="n">
-        <v>2.0072</v>
+        <v>2.0031</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1659</v>
+        <v>1.1507</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3637</v>
+        <v>0.3545</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8022</v>
+        <v>0.7962</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6885</v>
+        <v>-0.6756</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.8935</v>
+        <v>-1.8825</v>
       </c>
       <c r="O14" t="n">
-        <v>1.205</v>
+        <v>1.2069</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0447</v>
+        <v>2.0487</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1923</v>
+        <v>0.6388</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5718</v>
+        <v>0.3851</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.2537</v>
       </c>
       <c r="V14" t="n">
-        <v>1.6369</v>
+        <v>1.6342</v>
       </c>
       <c r="W14" t="n">
-        <v>1.6369</v>
+        <v>1.6342</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2581</v>
+        <v>2.0653</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0733</v>
+        <v>0.5107</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1848</v>
+        <v>1.5546</v>
       </c>
       <c r="G15" t="n">
-        <v>2.9234</v>
+        <v>2.9109</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.9265</v>
+        <v>-2.9289</v>
       </c>
       <c r="I15" t="n">
-        <v>5.8498</v>
+        <v>5.8398</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5074</v>
+        <v>2.481</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.9797</v>
+        <v>-1.9939</v>
       </c>
       <c r="L15" t="n">
-        <v>4.487</v>
+        <v>4.475</v>
       </c>
       <c r="M15" t="n">
-        <v>0.416</v>
+        <v>0.4299</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9468</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>1.3628</v>
+        <v>1.3648</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0447</v>
+        <v>2.0487</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.4149</v>
+        <v>-0.5969</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.2304</v>
+        <v>-0.7623</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1846</v>
+        <v>0.1655</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.9318</v>
+        <v>-0.9317</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. VILA</t>
+          <t>K. ROBERTSON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0076</v>
+        <v>1.8432</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2271</v>
+        <v>0.803</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2195</v>
+        <v>1.0403</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6611</v>
+        <v>2.1004</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2337</v>
+        <v>-1.351</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4274</v>
+        <v>3.4514</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9241</v>
+        <v>2.4734</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8122</v>
+        <v>-0.6173</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1118</v>
+        <v>3.0907</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.263</v>
+        <v>-0.3729</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5786</v>
+        <v>-0.7337</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3156</v>
+        <v>0.3608</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2272</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2272</v>
+        <v>1.1382</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1194</v>
+        <v>-0.3287</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3031</v>
+        <v>-0.5323</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1837</v>
+        <v>0.2036</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.07140000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. ROBERTSON</t>
+          <t>E. VILA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8183</v>
+        <v>0.6291</v>
       </c>
       <c r="E17" t="n">
-        <v>0.459</v>
+        <v>0.7498</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3593</v>
+        <v>-0.1207</v>
       </c>
       <c r="G17" t="n">
-        <v>2.0932</v>
+        <v>0.6627999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.36</v>
+        <v>0.2353</v>
       </c>
       <c r="I17" t="n">
-        <v>3.4532</v>
+        <v>0.4276</v>
       </c>
       <c r="J17" t="n">
-        <v>2.4783</v>
+        <v>0.9218</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6161</v>
+        <v>0.8101</v>
       </c>
       <c r="L17" t="n">
-        <v>3.0943</v>
+        <v>0.1117</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3851</v>
+        <v>-0.259</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7439</v>
+        <v>-0.5749</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3588</v>
+        <v>0.3159</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.2276</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1359</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1359</v>
+        <v>0.2276</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3423</v>
+        <v>-0.2614</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8833</v>
+        <v>-0.1721</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.459</v>
+        <v>-0.0893</v>
       </c>
       <c r="V17" t="n">
-        <v>0.0674</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0674</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. ALOCEN</t>
+          <t>A. ALBICY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.268</v>
+        <v>0.0566</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0909</v>
+        <v>-0.5013</v>
       </c>
       <c r="F18" t="n">
-        <v>0.823</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5587</v>
+        <v>-0.9816</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2058</v>
+        <v>-1.1409</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3528</v>
+        <v>0.1592</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3483</v>
+        <v>-0.3362</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3111</v>
+        <v>-0.1346</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0373</v>
+        <v>-0.2015</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2103</v>
+        <v>-0.6455</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1052</v>
+        <v>-1.0062</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3156</v>
+        <v>0.3608</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.8175</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2719</v>
+        <v>-1.3658</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4544</v>
+        <v>1.1382</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1004</v>
+        <v>0.1765</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2587</v>
+        <v>0.1111</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1583</v>
+        <v>0.0653</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. ALBICY</t>
+          <t>C. ALOCEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6357</v>
+        <v>-0.3632</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4887</v>
+        <v>-1.0996</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.147</v>
+        <v>0.7365</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9862</v>
+        <v>0.5623</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1466</v>
+        <v>0.2092</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1604</v>
+        <v>0.3531</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3306</v>
+        <v>0.3475</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1322</v>
+        <v>0.3103</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1984</v>
+        <v>0.0372</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6555</v>
+        <v>0.2148</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.0144</v>
+        <v>-0.1011</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3588</v>
+        <v>0.3159</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2272</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.3631</v>
+        <v>-2.2763</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1359</v>
+        <v>0.4553</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-0.1939</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1138</v>
+        <v>-0.2603</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6274</v>
+        <v>0.0664</v>
       </c>
       <c r="V19" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0054</v>
+        <v>-0.5917</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.8326</v>
+        <v>-2.8538</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8272</v>
+        <v>2.2621</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2125</v>
+        <v>-1.2063</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.5659</v>
+        <v>-2.5571</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3534</v>
+        <v>1.3508</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.2105</v>
+        <v>-1.2205</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.4162</v>
+        <v>-1.4209</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2057</v>
+        <v>0.2004</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0019</v>
+        <v>0.0142</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1497</v>
+        <v>-1.1362</v>
       </c>
       <c r="O20" t="n">
-        <v>1.1477</v>
+        <v>1.1504</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4544</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.4991</v>
+        <v>-2.5039</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0447</v>
+        <v>2.0487</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4298</v>
+        <v>-0.0196</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2143</v>
+        <v>-0.2189</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2156</v>
+        <v>0.1992</v>
       </c>
       <c r="V20" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. TOBEY</t>
+          <t>N. BRUSSINO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0263</v>
+        <v>-1.4202</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6841</v>
+        <v>-1.0978</v>
       </c>
       <c r="F21" t="n">
-        <v>1.6578</v>
+        <v>-0.3224</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2034</v>
+        <v>-1.6346</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4823</v>
+        <v>-3.9985</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6857</v>
+        <v>2.3639</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6269</v>
+        <v>-0.6865</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3171</v>
+        <v>-2.3172</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.944</v>
+        <v>1.6308</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4235</v>
+        <v>-0.9481000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1652</v>
+        <v>-1.6813</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2583</v>
+        <v>0.7331</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.1359</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2272</v>
+        <v>0.6829</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4724</v>
+        <v>-0.2636</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-0.135</v>
       </c>
       <c r="U21" t="n">
-        <v>1.1665</v>
+        <v>-0.1286</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1594</v>
+        <v>1.1609</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1594</v>
+        <v>0.07140000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. BRUSSINO</t>
+          <t>M. TOBEY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0882</v>
+        <v>-1.4361</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5581</v>
+        <v>-2.5771</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5301</v>
+        <v>1.141</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.6394</v>
+        <v>-0.2019</v>
       </c>
       <c r="H22" t="n">
-        <v>-4.0055</v>
+        <v>0.485</v>
       </c>
       <c r="I22" t="n">
-        <v>2.366</v>
+        <v>-0.6869</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6805</v>
+        <v>-0.6327</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.3149</v>
+        <v>0.3135</v>
       </c>
       <c r="L22" t="n">
-        <v>1.6344</v>
+        <v>-0.9463</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.959</v>
+        <v>0.4308</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.6906</v>
+        <v>0.1715</v>
       </c>
       <c r="O22" t="n">
-        <v>0.7317</v>
+        <v>0.2593</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6816</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6816</v>
+        <v>0.2276</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9258999999999999</v>
+        <v>0.0618</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6057</v>
+        <v>-0.5786</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3202</v>
+        <v>0.6404</v>
       </c>
       <c r="V22" t="n">
-        <v>1.1587</v>
+        <v>-0.1578</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0913</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.0674</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="23">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.1587</v>
+        <v>-1.9153</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.9178</v>
+        <v>-2.8048</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7591</v>
+        <v>0.8895</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.1251</v>
+        <v>-1.1232</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.6357</v>
+        <v>-1.6342</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5106000000000001</v>
+        <v>0.511</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.5232</v>
+        <v>-1.5248</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.5605</v>
+        <v>-1.562</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3982</v>
+        <v>0.4016</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0752</v>
+        <v>-0.0722</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4733</v>
+        <v>0.4738</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.4544</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5793</v>
+        <v>-0.3368</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2587</v>
+        <v>-0.1418</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3206</v>
+        <v>-0.195</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.3561</v>
+        <v>-4.1794</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.0449</v>
+        <v>-4.9393</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6888</v>
+        <v>0.7598</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.9016</v>
+        <v>-0.8997000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.5913</v>
+        <v>-0.5865</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3102</v>
+        <v>-0.3132</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.0819</v>
+        <v>-1.0856</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.0991</v>
+        <v>-1.1029</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1803</v>
+        <v>0.1859</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6086</v>
+        <v>-0.6037</v>
       </c>
       <c r="O24" t="n">
-        <v>0.7889</v>
+        <v>0.7896</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.7262</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.4078</v>
+        <v>-3.4145</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7282999999999999</v>
+        <v>-0.5481</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5553</v>
+        <v>-0.4392</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.173</v>
+        <v>-0.1089</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.238999999999999</v>
+        <v>-1.653099999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-11.6191</v>
+        <v>-11.7784</v>
       </c>
       <c r="F25" t="n">
-        <v>8.380100000000001</v>
+        <v>10.1255</v>
       </c>
       <c r="G25" t="n">
-        <v>0.6455999999999991</v>
+        <v>0.6641999999999991</v>
       </c>
       <c r="H25" t="n">
-        <v>-14.8394</v>
+        <v>-14.7956</v>
       </c>
       <c r="I25" t="n">
-        <v>15.4849</v>
+        <v>15.4598</v>
       </c>
       <c r="J25" t="n">
-        <v>1.9704</v>
+        <v>1.8881</v>
       </c>
       <c r="K25" t="n">
-        <v>-6.198200000000001</v>
+        <v>-6.2403</v>
       </c>
       <c r="L25" t="n">
-        <v>8.1685</v>
+        <v>8.128499999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.3247</v>
+        <v>-1.2239</v>
       </c>
       <c r="N25" t="n">
-        <v>-8.641300000000001</v>
+        <v>-8.555300000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>7.3165</v>
+        <v>7.3313</v>
       </c>
       <c r="P25" t="n">
-        <v>-5.6797</v>
+        <v>-5.690999999999999</v>
       </c>
       <c r="Q25" t="n">
-        <v>-17.0389</v>
+        <v>-17.0725</v>
       </c>
       <c r="R25" t="n">
-        <v>11.3595</v>
+        <v>11.3817</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.2504</v>
+        <v>-1.6719</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.7118</v>
+        <v>-2.7443</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5387999999999998</v>
+        <v>1.0723</v>
       </c>
       <c r="V25" t="n">
-        <v>5.0457</v>
+        <v>5.0455</v>
       </c>
       <c r="W25" t="n">
-        <v>6.1615</v>
+        <v>6.149999999999999</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.1159</v>
+        <v>-1.1045</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104740_W32.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104740_W32.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104740_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104740_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104740_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104740_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104740_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104740_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104740_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104740_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104740_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104740_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104740_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-6.149900000000001</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104740_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104740_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0.07140000000000001</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104740_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104740_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104740_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104740_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104740_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0.07140000000000001</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104740_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104740_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104740_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104740_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-1.1045</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
